--- a/data/2026-05-04/BallparkPal_Pitchers.xlsx
+++ b/data/2026-05-04/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="110">
   <si>
     <t>GamePk</t>
   </si>
@@ -87,6 +87,264 @@
   </si>
   <si>
     <t>StolenBasesAllowed</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Lauer</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>7:45</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Leahy</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Chad Patrick</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>9:40</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Gilbert</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>JR Ritchie</t>
+  </si>
+  <si>
+    <t>Ritchie</t>
+  </si>
+  <si>
+    <t>9:45</t>
+  </si>
+  <si>
+    <t>Randy Vasquez</t>
+  </si>
+  <si>
+    <t>Vasquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>Trevor McDonald</t>
+  </si>
+  <si>
+    <t>McDonald</t>
+  </si>
+  <si>
+    <t>7:05</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Baz</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Schlittler</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Nola</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Junk</t>
+  </si>
+  <si>
+    <t>9:38</t>
+  </si>
+  <si>
+    <t>Davis Martin</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>Jose Soriano</t>
+  </si>
+  <si>
+    <t>Soriano</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Wacha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Bibee</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>Steven Okert</t>
+  </si>
+  <si>
+    <t>Okert</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Yamamoto</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Skubal</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>Tolle</t>
+  </si>
+  <si>
+    <t>5:40</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Sugano</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>Tobias Myers</t>
+  </si>
+  <si>
+    <t>Myers</t>
+  </si>
+  <si>
+    <t>Edward Cabrera</t>
+  </si>
+  <si>
+    <t>Cabrera</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>Chase Petty</t>
+  </si>
+  <si>
+    <t>Petty</t>
   </si>
 </sst>
 </file>
@@ -426,7 +684,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -501,6 +759,1782 @@
       </c>
       <c r="X1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2">
+        <v>822984</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>607259</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2">
+        <v>19.916</v>
+      </c>
+      <c r="L2">
+        <v>4.864</v>
+      </c>
+      <c r="M2">
+        <v>0.229</v>
+      </c>
+      <c r="N2">
+        <v>0.29</v>
+      </c>
+      <c r="O2">
+        <v>0.481</v>
+      </c>
+      <c r="P2">
+        <v>0.182</v>
+      </c>
+      <c r="Q2">
+        <v>10.928</v>
+      </c>
+      <c r="R2">
+        <v>20.169</v>
+      </c>
+      <c r="S2">
+        <v>2.011</v>
+      </c>
+      <c r="T2">
+        <v>4.426</v>
+      </c>
+      <c r="U2">
+        <v>3.169</v>
+      </c>
+      <c r="V2">
+        <v>0.988</v>
+      </c>
+      <c r="W2">
+        <v>0.717</v>
+      </c>
+      <c r="X2">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3">
+        <v>822984</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>641778</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>18.805</v>
+      </c>
+      <c r="L3">
+        <v>4.393</v>
+      </c>
+      <c r="M3">
+        <v>0.113</v>
+      </c>
+      <c r="N3">
+        <v>0.297</v>
+      </c>
+      <c r="O3">
+        <v>0.591</v>
+      </c>
+      <c r="P3">
+        <v>0.076</v>
+      </c>
+      <c r="Q3">
+        <v>9.025</v>
+      </c>
+      <c r="R3">
+        <v>17.383</v>
+      </c>
+      <c r="S3">
+        <v>2.095</v>
+      </c>
+      <c r="T3">
+        <v>4.365</v>
+      </c>
+      <c r="U3">
+        <v>3.169</v>
+      </c>
+      <c r="V3">
+        <v>1.402</v>
+      </c>
+      <c r="W3">
+        <v>0.512</v>
+      </c>
+      <c r="X3">
+        <v>0.415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4">
+        <v>823064</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>681517</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>19.502</v>
+      </c>
+      <c r="L4">
+        <v>4.398</v>
+      </c>
+      <c r="M4">
+        <v>0.156</v>
+      </c>
+      <c r="N4">
+        <v>0.328</v>
+      </c>
+      <c r="O4">
+        <v>0.516</v>
+      </c>
+      <c r="P4">
+        <v>0.093</v>
+      </c>
+      <c r="Q4">
+        <v>8.383</v>
+      </c>
+      <c r="R4">
+        <v>17.195</v>
+      </c>
+      <c r="S4">
+        <v>2.339</v>
+      </c>
+      <c r="T4">
+        <v>4.853</v>
+      </c>
+      <c r="U4">
+        <v>3.236</v>
+      </c>
+      <c r="V4">
+        <v>1.701</v>
+      </c>
+      <c r="W4">
+        <v>0.535</v>
+      </c>
+      <c r="X4">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5">
+        <v>823064</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>694477</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5">
+        <v>18.776</v>
+      </c>
+      <c r="L5">
+        <v>4.315</v>
+      </c>
+      <c r="M5">
+        <v>0.121</v>
+      </c>
+      <c r="N5">
+        <v>0.24</v>
+      </c>
+      <c r="O5">
+        <v>0.639</v>
+      </c>
+      <c r="P5">
+        <v>0.073</v>
+      </c>
+      <c r="Q5">
+        <v>10.185</v>
+      </c>
+      <c r="R5">
+        <v>19.273</v>
+      </c>
+      <c r="S5">
+        <v>2.165</v>
+      </c>
+      <c r="T5">
+        <v>4.118</v>
+      </c>
+      <c r="U5">
+        <v>3.935</v>
+      </c>
+      <c r="V5">
+        <v>1.793</v>
+      </c>
+      <c r="W5">
+        <v>0.624</v>
+      </c>
+      <c r="X5">
+        <v>0.331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6">
+        <v>823143</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6">
+        <v>669302</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6">
+        <v>23.555</v>
+      </c>
+      <c r="L6">
+        <v>5.666</v>
+      </c>
+      <c r="M6">
+        <v>0.342</v>
+      </c>
+      <c r="N6">
+        <v>0.274</v>
+      </c>
+      <c r="O6">
+        <v>0.383</v>
+      </c>
+      <c r="P6">
+        <v>0.438</v>
+      </c>
+      <c r="Q6">
+        <v>16.558</v>
+      </c>
+      <c r="R6">
+        <v>30.433</v>
+      </c>
+      <c r="S6">
+        <v>2.39</v>
+      </c>
+      <c r="T6">
+        <v>5.413</v>
+      </c>
+      <c r="U6">
+        <v>5.599</v>
+      </c>
+      <c r="V6">
+        <v>1.276</v>
+      </c>
+      <c r="W6">
+        <v>0.838</v>
+      </c>
+      <c r="X6">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7">
+        <v>823143</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>702275</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7">
+        <v>23.056</v>
+      </c>
+      <c r="L7">
+        <v>5.274</v>
+      </c>
+      <c r="M7">
+        <v>0.181</v>
+      </c>
+      <c r="N7">
+        <v>0.378</v>
+      </c>
+      <c r="O7">
+        <v>0.44</v>
+      </c>
+      <c r="P7">
+        <v>0.342</v>
+      </c>
+      <c r="Q7">
+        <v>13.542</v>
+      </c>
+      <c r="R7">
+        <v>26.409</v>
+      </c>
+      <c r="S7">
+        <v>2.723</v>
+      </c>
+      <c r="T7">
+        <v>4.862</v>
+      </c>
+      <c r="U7">
+        <v>5.433</v>
+      </c>
+      <c r="V7">
+        <v>2.595</v>
+      </c>
+      <c r="W7">
+        <v>0.879</v>
+      </c>
+      <c r="X7">
+        <v>0.399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8">
+        <v>823228</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>681190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8">
+        <v>22.502</v>
+      </c>
+      <c r="L8">
+        <v>5.355</v>
+      </c>
+      <c r="M8">
+        <v>0.226</v>
+      </c>
+      <c r="N8">
+        <v>0.271</v>
+      </c>
+      <c r="O8">
+        <v>0.503</v>
+      </c>
+      <c r="P8">
+        <v>0.379</v>
+      </c>
+      <c r="Q8">
+        <v>13.839</v>
+      </c>
+      <c r="R8">
+        <v>26.225</v>
+      </c>
+      <c r="S8">
+        <v>2.035</v>
+      </c>
+      <c r="T8">
+        <v>5.026</v>
+      </c>
+      <c r="U8">
+        <v>4.464</v>
+      </c>
+      <c r="V8">
+        <v>1.619</v>
+      </c>
+      <c r="W8">
+        <v>0.428</v>
+      </c>
+      <c r="X8">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9">
+        <v>823228</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>686790</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9">
+        <v>20.858</v>
+      </c>
+      <c r="L9">
+        <v>5.017</v>
+      </c>
+      <c r="M9">
+        <v>0.211</v>
+      </c>
+      <c r="N9">
+        <v>0.316</v>
+      </c>
+      <c r="O9">
+        <v>0.472</v>
+      </c>
+      <c r="P9">
+        <v>0.257</v>
+      </c>
+      <c r="Q9">
+        <v>13.711</v>
+      </c>
+      <c r="R9">
+        <v>25.155</v>
+      </c>
+      <c r="S9">
+        <v>1.9</v>
+      </c>
+      <c r="T9">
+        <v>4.838</v>
+      </c>
+      <c r="U9">
+        <v>4.503</v>
+      </c>
+      <c r="V9">
+        <v>1.216</v>
+      </c>
+      <c r="W9">
+        <v>0.394</v>
+      </c>
+      <c r="X9">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10">
+        <v>823552</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>669358</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10">
+        <v>22.211</v>
+      </c>
+      <c r="L10">
+        <v>4.837</v>
+      </c>
+      <c r="M10">
+        <v>0.097</v>
+      </c>
+      <c r="N10">
+        <v>0.508</v>
+      </c>
+      <c r="O10">
+        <v>0.395</v>
+      </c>
+      <c r="P10">
+        <v>0.221</v>
+      </c>
+      <c r="Q10">
+        <v>10.302</v>
+      </c>
+      <c r="R10">
+        <v>21.693</v>
+      </c>
+      <c r="S10">
+        <v>2.88</v>
+      </c>
+      <c r="T10">
+        <v>4.897</v>
+      </c>
+      <c r="U10">
+        <v>4.785</v>
+      </c>
+      <c r="V10">
+        <v>3.072</v>
+      </c>
+      <c r="W10">
+        <v>0.697</v>
+      </c>
+      <c r="X10">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11">
+        <v>823552</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>693645</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11">
+        <v>25.224</v>
+      </c>
+      <c r="L11">
+        <v>6.405</v>
+      </c>
+      <c r="M11">
+        <v>0.521</v>
+      </c>
+      <c r="N11">
+        <v>0.163</v>
+      </c>
+      <c r="O11">
+        <v>0.315</v>
+      </c>
+      <c r="P11">
+        <v>0.655</v>
+      </c>
+      <c r="Q11">
+        <v>24.301</v>
+      </c>
+      <c r="R11">
+        <v>41.967</v>
+      </c>
+      <c r="S11">
+        <v>1.841</v>
+      </c>
+      <c r="T11">
+        <v>4.691</v>
+      </c>
+      <c r="U11">
+        <v>7.509</v>
+      </c>
+      <c r="V11">
+        <v>1.345</v>
+      </c>
+      <c r="W11">
+        <v>0.664</v>
+      </c>
+      <c r="X11">
+        <v>0.356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12">
+        <v>823874</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>605400</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12">
+        <v>22.241</v>
+      </c>
+      <c r="L12">
+        <v>5.409</v>
+      </c>
+      <c r="M12">
+        <v>0.252</v>
+      </c>
+      <c r="N12">
+        <v>0.257</v>
+      </c>
+      <c r="O12">
+        <v>0.491</v>
+      </c>
+      <c r="P12">
+        <v>0.398</v>
+      </c>
+      <c r="Q12">
+        <v>15.991</v>
+      </c>
+      <c r="R12">
+        <v>29.092</v>
+      </c>
+      <c r="S12">
+        <v>1.999</v>
+      </c>
+      <c r="T12">
+        <v>4.328</v>
+      </c>
+      <c r="U12">
+        <v>5.253</v>
+      </c>
+      <c r="V12">
+        <v>1.852</v>
+      </c>
+      <c r="W12">
+        <v>0.507</v>
+      </c>
+      <c r="X12">
+        <v>0.577</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13">
+        <v>823874</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13">
+        <v>676083</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13">
+        <v>23.844</v>
+      </c>
+      <c r="L13">
+        <v>5.719</v>
+      </c>
+      <c r="M13">
+        <v>0.249</v>
+      </c>
+      <c r="N13">
+        <v>0.396</v>
+      </c>
+      <c r="O13">
+        <v>0.355</v>
+      </c>
+      <c r="P13">
+        <v>0.443</v>
+      </c>
+      <c r="Q13">
+        <v>11.812</v>
+      </c>
+      <c r="R13">
+        <v>23.482</v>
+      </c>
+      <c r="S13">
+        <v>2.501</v>
+      </c>
+      <c r="T13">
+        <v>5.622</v>
+      </c>
+      <c r="U13">
+        <v>3.521</v>
+      </c>
+      <c r="V13">
+        <v>1.234</v>
+      </c>
+      <c r="W13">
+        <v>0.664</v>
+      </c>
+      <c r="X13">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14">
+        <v>824039</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14">
+        <v>663436</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14">
+        <v>23.18</v>
+      </c>
+      <c r="L14">
+        <v>5.328</v>
+      </c>
+      <c r="M14">
+        <v>0.165</v>
+      </c>
+      <c r="N14">
+        <v>0.418</v>
+      </c>
+      <c r="O14">
+        <v>0.417</v>
+      </c>
+      <c r="P14">
+        <v>0.346</v>
+      </c>
+      <c r="Q14">
+        <v>12.493</v>
+      </c>
+      <c r="R14">
+        <v>24.829</v>
+      </c>
+      <c r="S14">
+        <v>2.823</v>
+      </c>
+      <c r="T14">
+        <v>5.616</v>
+      </c>
+      <c r="U14">
+        <v>4.98</v>
+      </c>
+      <c r="V14">
+        <v>1.854</v>
+      </c>
+      <c r="W14">
+        <v>0.721</v>
+      </c>
+      <c r="X14">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15">
+        <v>824039</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>667755</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15">
+        <v>23.303</v>
+      </c>
+      <c r="L15">
+        <v>5.597</v>
+      </c>
+      <c r="M15">
+        <v>0.371</v>
+      </c>
+      <c r="N15">
+        <v>0.216</v>
+      </c>
+      <c r="O15">
+        <v>0.412</v>
+      </c>
+      <c r="P15">
+        <v>0.444</v>
+      </c>
+      <c r="Q15">
+        <v>19.502</v>
+      </c>
+      <c r="R15">
+        <v>35.052</v>
+      </c>
+      <c r="S15">
+        <v>1.912</v>
+      </c>
+      <c r="T15">
+        <v>4.401</v>
+      </c>
+      <c r="U15">
+        <v>6.663</v>
+      </c>
+      <c r="V15">
+        <v>2.469</v>
+      </c>
+      <c r="W15">
+        <v>0.408</v>
+      </c>
+      <c r="X15">
+        <v>0.221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16">
+        <v>824120</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16">
+        <v>608379</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16">
+        <v>23.79</v>
+      </c>
+      <c r="L16">
+        <v>5.553</v>
+      </c>
+      <c r="M16">
+        <v>0.316</v>
+      </c>
+      <c r="N16">
+        <v>0.287</v>
+      </c>
+      <c r="O16">
+        <v>0.397</v>
+      </c>
+      <c r="P16">
+        <v>0.394</v>
+      </c>
+      <c r="Q16">
+        <v>11.138</v>
+      </c>
+      <c r="R16">
+        <v>22.748</v>
+      </c>
+      <c r="S16">
+        <v>2.766</v>
+      </c>
+      <c r="T16">
+        <v>5.38</v>
+      </c>
+      <c r="U16">
+        <v>3.639</v>
+      </c>
+      <c r="V16">
+        <v>1.927</v>
+      </c>
+      <c r="W16">
+        <v>0.856</v>
+      </c>
+      <c r="X16">
+        <v>0.467</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>824120</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17">
+        <v>676440</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17">
+        <v>22.631</v>
+      </c>
+      <c r="L17">
+        <v>5.116</v>
+      </c>
+      <c r="M17">
+        <v>0.173</v>
+      </c>
+      <c r="N17">
+        <v>0.351</v>
+      </c>
+      <c r="O17">
+        <v>0.476</v>
+      </c>
+      <c r="P17">
+        <v>0.277</v>
+      </c>
+      <c r="Q17">
+        <v>8.86</v>
+      </c>
+      <c r="R17">
+        <v>19.192</v>
+      </c>
+      <c r="S17">
+        <v>3.055</v>
+      </c>
+      <c r="T17">
+        <v>5.703</v>
+      </c>
+      <c r="U17">
+        <v>3.622</v>
+      </c>
+      <c r="V17">
+        <v>1.765</v>
+      </c>
+      <c r="W17">
+        <v>0.816</v>
+      </c>
+      <c r="X17">
+        <v>0.615</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>824201</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18">
+        <v>595345</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18">
+        <v>4.723</v>
+      </c>
+      <c r="L18">
+        <v>1.095</v>
+      </c>
+      <c r="M18">
+        <v>0.0</v>
+      </c>
+      <c r="N18">
+        <v>0.16</v>
+      </c>
+      <c r="O18">
+        <v>0.84</v>
+      </c>
+      <c r="P18">
+        <v>0.0</v>
+      </c>
+      <c r="Q18">
+        <v>2.68</v>
+      </c>
+      <c r="R18">
+        <v>4.889</v>
+      </c>
+      <c r="S18">
+        <v>0.459</v>
+      </c>
+      <c r="T18">
+        <v>0.973</v>
+      </c>
+      <c r="U18">
+        <v>0.994</v>
+      </c>
+      <c r="V18">
+        <v>0.448</v>
+      </c>
+      <c r="W18">
+        <v>0.196</v>
+      </c>
+      <c r="X18">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
+        <v>824201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19">
+        <v>808967</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19">
+        <v>24.282</v>
+      </c>
+      <c r="L19">
+        <v>5.897</v>
+      </c>
+      <c r="M19">
+        <v>0.297</v>
+      </c>
+      <c r="N19">
+        <v>0.245</v>
+      </c>
+      <c r="O19">
+        <v>0.458</v>
+      </c>
+      <c r="P19">
+        <v>0.545</v>
+      </c>
+      <c r="Q19">
+        <v>16.524</v>
+      </c>
+      <c r="R19">
+        <v>30.849</v>
+      </c>
+      <c r="S19">
+        <v>2.299</v>
+      </c>
+      <c r="T19">
+        <v>4.931</v>
+      </c>
+      <c r="U19">
+        <v>5.364</v>
+      </c>
+      <c r="V19">
+        <v>1.909</v>
+      </c>
+      <c r="W19">
+        <v>0.671</v>
+      </c>
+      <c r="X19">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>824283</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>669373</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>94</v>
+      </c>
+      <c r="K20">
+        <v>25.78</v>
+      </c>
+      <c r="L20">
+        <v>6.212</v>
+      </c>
+      <c r="M20">
+        <v>0.438</v>
+      </c>
+      <c r="N20">
+        <v>0.235</v>
+      </c>
+      <c r="O20">
+        <v>0.327</v>
+      </c>
+      <c r="P20">
+        <v>0.59</v>
+      </c>
+      <c r="Q20">
+        <v>20.79</v>
+      </c>
+      <c r="R20">
+        <v>37.781</v>
+      </c>
+      <c r="S20">
+        <v>2.353</v>
+      </c>
+      <c r="T20">
+        <v>6.239</v>
+      </c>
+      <c r="U20">
+        <v>7.072</v>
+      </c>
+      <c r="V20">
+        <v>1.15</v>
+      </c>
+      <c r="W20">
+        <v>0.491</v>
+      </c>
+      <c r="X20">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
+        <v>824283</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
+        <v>801139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21">
+        <v>18.542</v>
+      </c>
+      <c r="L21">
+        <v>4.046</v>
+      </c>
+      <c r="M21">
+        <v>0.077</v>
+      </c>
+      <c r="N21">
+        <v>0.374</v>
+      </c>
+      <c r="O21">
+        <v>0.549</v>
+      </c>
+      <c r="P21">
+        <v>0.045</v>
+      </c>
+      <c r="Q21">
+        <v>10.251</v>
+      </c>
+      <c r="R21">
+        <v>19.947</v>
+      </c>
+      <c r="S21">
+        <v>2.189</v>
+      </c>
+      <c r="T21">
+        <v>3.946</v>
+      </c>
+      <c r="U21">
+        <v>4.579</v>
+      </c>
+      <c r="V21">
+        <v>2.621</v>
+      </c>
+      <c r="W21">
+        <v>0.412</v>
+      </c>
+      <c r="X21">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22">
+        <v>824363</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22">
+        <v>608372</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22">
+        <v>22.873</v>
+      </c>
+      <c r="L22">
+        <v>5.184</v>
+      </c>
+      <c r="M22">
+        <v>0.285</v>
+      </c>
+      <c r="N22">
+        <v>0.295</v>
+      </c>
+      <c r="O22">
+        <v>0.419</v>
+      </c>
+      <c r="P22">
+        <v>0.266</v>
+      </c>
+      <c r="Q22">
+        <v>8.018</v>
+      </c>
+      <c r="R22">
+        <v>17.956</v>
+      </c>
+      <c r="S22">
+        <v>3.159</v>
+      </c>
+      <c r="T22">
+        <v>5.964</v>
+      </c>
+      <c r="U22">
+        <v>3.036</v>
+      </c>
+      <c r="V22">
+        <v>1.608</v>
+      </c>
+      <c r="W22">
+        <v>0.969</v>
+      </c>
+      <c r="X22">
+        <v>0.454</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23">
+        <v>824363</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23">
+        <v>668964</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>7.308</v>
+      </c>
+      <c r="L23">
+        <v>1.69</v>
+      </c>
+      <c r="M23">
+        <v>0.002</v>
+      </c>
+      <c r="N23">
+        <v>0.14</v>
+      </c>
+      <c r="O23">
+        <v>0.858</v>
+      </c>
+      <c r="P23">
+        <v>0.001</v>
+      </c>
+      <c r="Q23">
+        <v>3.021</v>
+      </c>
+      <c r="R23">
+        <v>5.942</v>
+      </c>
+      <c r="S23">
+        <v>0.906</v>
+      </c>
+      <c r="T23">
+        <v>1.874</v>
+      </c>
+      <c r="U23">
+        <v>1.192</v>
+      </c>
+      <c r="V23">
+        <v>0.395</v>
+      </c>
+      <c r="W23">
+        <v>0.301</v>
+      </c>
+      <c r="X23">
+        <v>0.072</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24">
+        <v>824684</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24">
+        <v>665795</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24">
+        <v>23.223</v>
+      </c>
+      <c r="L24">
+        <v>5.215</v>
+      </c>
+      <c r="M24">
+        <v>0.354</v>
+      </c>
+      <c r="N24">
+        <v>0.214</v>
+      </c>
+      <c r="O24">
+        <v>0.432</v>
+      </c>
+      <c r="P24">
+        <v>0.296</v>
+      </c>
+      <c r="Q24">
+        <v>13.348</v>
+      </c>
+      <c r="R24">
+        <v>26.275</v>
+      </c>
+      <c r="S24">
+        <v>3.06</v>
+      </c>
+      <c r="T24">
+        <v>5.136</v>
+      </c>
+      <c r="U24">
+        <v>5.5</v>
+      </c>
+      <c r="V24">
+        <v>2.674</v>
+      </c>
+      <c r="W24">
+        <v>0.954</v>
+      </c>
+      <c r="X24">
+        <v>0.618</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25">
+        <v>824684</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25">
+        <v>695534</v>
+      </c>
+      <c r="E25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25">
+        <v>18.632</v>
+      </c>
+      <c r="L25">
+        <v>3.785</v>
+      </c>
+      <c r="M25">
+        <v>0.056</v>
+      </c>
+      <c r="N25">
+        <v>0.384</v>
+      </c>
+      <c r="O25">
+        <v>0.561</v>
+      </c>
+      <c r="P25">
+        <v>0.029</v>
+      </c>
+      <c r="Q25">
+        <v>4.74</v>
+      </c>
+      <c r="R25">
+        <v>12.552</v>
+      </c>
+      <c r="S25">
+        <v>3.181</v>
+      </c>
+      <c r="T25">
+        <v>4.586</v>
+      </c>
+      <c r="U25">
+        <v>3.431</v>
+      </c>
+      <c r="V25">
+        <v>2.91</v>
+      </c>
+      <c r="W25">
+        <v>0.884</v>
+      </c>
+      <c r="X25">
+        <v>0.323</v>
       </c>
     </row>
   </sheetData>
